--- a/pantalla-nueva-prueba.xlsx
+++ b/pantalla-nueva-prueba.xlsx
@@ -555,7 +555,7 @@
         <v>156000</v>
       </c>
       <c r="S2">
-        <v>88000</v>
+        <v>42000</v>
       </c>
       <c r="T2">
         <v>42000</v>
